--- a/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16500" windowHeight="9510" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16500" windowHeight="9510" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
     <sheet name="Router" sheetId="3" r:id="rId2"/>
+    <sheet name="公共服" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="34">
   <si>
     <t>Id</t>
   </si>
@@ -99,6 +100,30 @@
   </si>
   <si>
     <t>Router04</t>
+  </si>
+  <si>
+    <t>#</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏一区启动的fiber</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LoginCenter</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Realm</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>公共服，区服id比较大</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -475,18 +500,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:H12"/>
+  <dimension ref="B1:H12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="5" width="12.625" style="3" customWidth="1"/>
+    <col min="3" max="4" width="12.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.25" style="3" customWidth="1"/>
     <col min="6" max="6" width="15.375" style="3" customWidth="1"/>
     <col min="7" max="8" width="13.125" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E1" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -506,7 +537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -526,7 +557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
@@ -546,7 +577,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="3:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="C6" s="5">
         <v>1</v>
       </c>
@@ -566,7 +600,7 @@
         <v>30002</v>
       </c>
     </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C7" s="5">
         <v>2</v>
       </c>
@@ -586,7 +620,7 @@
         <v>30003</v>
       </c>
     </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C8" s="5">
         <v>3</v>
       </c>
@@ -606,7 +640,7 @@
         <v>30004</v>
       </c>
     </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C9" s="5">
         <v>4</v>
       </c>
@@ -624,7 +658,7 @@
       </c>
       <c r="H9" s="5"/>
     </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C10" s="5">
         <v>5</v>
       </c>
@@ -642,7 +676,7 @@
       </c>
       <c r="H10" s="5"/>
     </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C11" s="5">
         <v>6</v>
       </c>
@@ -660,7 +694,7 @@
       </c>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C12" s="5">
         <v>7</v>
       </c>
@@ -863,4 +897,121 @@
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C1:H7"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="5" max="5" width="21.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="3:8" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="C3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="C4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="C6" s="5">
+        <v>401</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1000</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="3:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="C7" s="5">
+        <v>402</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1000</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="5">
+        <v>30002</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16500" windowHeight="9510" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16500" windowHeight="9495"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="37">
   <si>
     <t>Id</t>
   </si>
@@ -123,6 +123,17 @@
   </si>
   <si>
     <t>公共服，区服id比较大</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnitCache</t>
+  </si>
+  <si>
+    <t>UnitCache</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mail</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -500,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:H12"/>
+  <dimension ref="B1:H14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -602,7 +613,7 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="5">
         <v>1</v>
@@ -622,7 +633,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C8" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="5">
         <v>1</v>
@@ -642,7 +653,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C9" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="5">
         <v>1</v>
@@ -659,58 +670,92 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C10" s="5">
-        <v>5</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="C10" s="3">
+        <v>4</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
         <v>1</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C11" s="5">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
         <v>6</v>
       </c>
-      <c r="D11" s="5">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C13" s="5">
+        <v>7</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C12" s="5">
-        <v>7</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1</v>
-      </c>
-      <c r="E12" s="5">
-        <v>1</v>
-      </c>
-      <c r="F12" s="3" t="s">
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="5">
+        <v>8</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="39">
   <si>
     <t>Id</t>
   </si>
@@ -134,6 +134,14 @@
   </si>
   <si>
     <t>Mail</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>二区</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>一区</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -511,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:H14"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -523,12 +531,12 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -548,7 +556,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -568,7 +576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
@@ -588,7 +596,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B6" s="1" t="s">
         <v>28</v>
       </c>
@@ -611,7 +619,10 @@
         <v>30002</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="C7" s="5">
         <v>1</v>
       </c>
@@ -628,10 +639,10 @@
         <v>15</v>
       </c>
       <c r="H7" s="5">
-        <v>30003</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+        <v>30010</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C8" s="5">
         <v>2</v>
       </c>
@@ -648,10 +659,10 @@
         <v>16</v>
       </c>
       <c r="H8" s="5">
-        <v>30004</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+        <v>30011</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" s="5">
         <v>3</v>
       </c>
@@ -669,8 +680,8 @@
       </c>
       <c r="H9" s="5"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C10" s="3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C10" s="5">
         <v>4</v>
       </c>
       <c r="D10" s="3">
@@ -687,7 +698,7 @@
       </c>
       <c r="H10" s="5"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C11" s="5">
         <v>5</v>
       </c>
@@ -705,8 +716,8 @@
       </c>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C12" s="3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C12" s="5">
         <v>6</v>
       </c>
       <c r="D12" s="3">
@@ -723,7 +734,7 @@
       </c>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C13" s="5">
         <v>7</v>
       </c>
@@ -740,7 +751,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C14" s="5">
         <v>8</v>
       </c>
@@ -754,6 +765,155 @@
         <v>19</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="5">
+        <v>9</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="5">
+        <v>30020</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C16" s="5">
+        <v>10</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5">
+        <v>2</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="5">
+        <v>30021</v>
+      </c>
+    </row>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C17" s="5">
+        <v>11</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C18" s="5">
+        <v>12</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C19" s="5">
+        <v>13</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C20" s="5">
+        <v>14</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C21" s="5">
+        <v>15</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C22" s="5">
+        <v>16</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5">
+        <v>2</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>21</v>
       </c>
     </row>

--- a/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="40">
   <si>
     <t>Id</t>
   </si>
@@ -142,6 +142,10 @@
   </si>
   <si>
     <t>一区</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rank</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -519,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -769,9 +773,6 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="C15" s="5">
         <v>9</v>
       </c>
@@ -779,19 +780,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="5">
-        <v>30020</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="C16" s="5">
         <v>10</v>
       </c>
@@ -805,10 +806,10 @@
         <v>14</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H16" s="5">
-        <v>30021</v>
+        <v>30020</v>
       </c>
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.3">
@@ -822,28 +823,30 @@
         <v>2</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="H17" s="5">
+        <v>30021</v>
+      </c>
     </row>
     <row r="18" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C18" s="5">
         <v>12</v>
       </c>
-      <c r="D18" s="3">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="D18" s="5">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5">
         <v>2</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H18" s="5"/>
     </row>
@@ -851,17 +854,17 @@
       <c r="C19" s="5">
         <v>13</v>
       </c>
-      <c r="D19" s="5">
-        <v>1</v>
-      </c>
-      <c r="E19" s="5">
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
         <v>2</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H19" s="5"/>
     </row>
@@ -869,17 +872,17 @@
       <c r="C20" s="5">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="5">
         <v>1</v>
       </c>
       <c r="E20" s="5">
         <v>2</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H20" s="5"/>
     </row>
@@ -890,31 +893,66 @@
       <c r="D21" s="3">
         <v>1</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="5">
         <v>2</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C22" s="5">
         <v>16</v>
       </c>
-      <c r="D22" s="5">
-        <v>1</v>
-      </c>
-      <c r="E22" s="5">
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3">
         <v>2</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C23" s="5">
+        <v>17</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <v>18</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="42">
   <si>
     <t>Id</t>
   </si>
@@ -146,6 +146,14 @@
   </si>
   <si>
     <t>Rank</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Param</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -523,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -535,12 +543,12 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -559,8 +567,11 @@
       <c r="H3" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -579,8 +590,11 @@
       <c r="H4" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
@@ -599,8 +613,11 @@
       <c r="H5" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B6" s="1" t="s">
         <v>28</v>
       </c>
@@ -622,8 +639,9 @@
       <c r="H6" s="5">
         <v>30002</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>38</v>
       </c>
@@ -645,8 +663,9 @@
       <c r="H7" s="5">
         <v>30010</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C8" s="5">
         <v>2</v>
       </c>
@@ -665,8 +684,9 @@
       <c r="H8" s="5">
         <v>30011</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C9" s="5">
         <v>3</v>
       </c>
@@ -683,8 +703,9 @@
         <v>17</v>
       </c>
       <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C10" s="5">
         <v>4</v>
       </c>
@@ -701,8 +722,9 @@
         <v>34</v>
       </c>
       <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C11" s="5">
         <v>5</v>
       </c>
@@ -719,8 +741,9 @@
         <v>18</v>
       </c>
       <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C12" s="5">
         <v>6</v>
       </c>
@@ -737,8 +760,9 @@
         <v>36</v>
       </c>
       <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C13" s="5">
         <v>7</v>
       </c>
@@ -754,8 +778,11 @@
       <c r="G13" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I13" s="3">
+        <v>11001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C14" s="5">
         <v>8</v>
       </c>
@@ -771,8 +798,11 @@
       <c r="G14" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I14" s="3">
+        <v>11002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C15" s="5">
         <v>9</v>
       </c>
@@ -788,8 +818,9 @@
       <c r="G15" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>37</v>
       </c>
@@ -811,8 +842,9 @@
       <c r="H16" s="5">
         <v>30020</v>
       </c>
-    </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C17" s="5">
         <v>11</v>
       </c>
@@ -831,8 +863,9 @@
       <c r="H17" s="5">
         <v>30021</v>
       </c>
-    </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C18" s="5">
         <v>12</v>
       </c>
@@ -849,8 +882,9 @@
         <v>17</v>
       </c>
       <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C19" s="5">
         <v>13</v>
       </c>
@@ -867,8 +901,9 @@
         <v>34</v>
       </c>
       <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C20" s="5">
         <v>14</v>
       </c>
@@ -885,8 +920,9 @@
         <v>18</v>
       </c>
       <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C21" s="5">
         <v>15</v>
       </c>
@@ -903,8 +939,9 @@
         <v>36</v>
       </c>
       <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C22" s="5">
         <v>16</v>
       </c>
@@ -920,8 +957,9 @@
       <c r="G22" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C23" s="5">
         <v>17</v>
       </c>
@@ -937,8 +975,9 @@
       <c r="G23" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C24" s="3">
         <v>18</v>
       </c>
@@ -954,6 +993,7 @@
       <c r="G24" s="3" t="s">
         <v>39</v>
       </c>
+      <c r="I24" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="45">
   <si>
     <t>Id</t>
   </si>
@@ -102,58 +102,70 @@
     <t>Router04</t>
   </si>
   <si>
+    <t>游戏一区启动的fiber</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LoginCenter</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Realm</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>公共服，区服id比较大</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnitCache</t>
+  </si>
+  <si>
+    <t>UnitCache</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mail</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>二区</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>一区</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rank</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t># 1服</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t># 2服</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>#</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>游戏一区启动的fiber</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Id</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LoginCenter</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Realm</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>公共服，区服id比较大</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnitCache</t>
-  </si>
-  <si>
-    <t>UnitCache</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mail</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>二区</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>一区</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rank</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Param</t>
+    <t>#</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapManager</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -531,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -543,12 +555,12 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E1" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -567,11 +579,8 @@
       <c r="H3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -590,11 +599,8 @@
       <c r="H4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
@@ -613,13 +619,10 @@
       <c r="H5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B6" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C6" s="5">
         <v>1</v>
@@ -639,35 +642,24 @@
       <c r="H6" s="5">
         <v>30002</v>
       </c>
-      <c r="I6" s="5"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="5">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="5">
-        <v>30010</v>
-      </c>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="C8" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="5">
         <v>1</v>
@@ -679,233 +671,213 @@
         <v>14</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="5">
+        <v>30010</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="5">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H9" s="5">
         <v>30011</v>
       </c>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="5">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C10" s="5">
         <v>3</v>
       </c>
-      <c r="D9" s="5">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="5">
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C11" s="5">
         <v>4</v>
       </c>
-      <c r="D10" s="3">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C12" s="5">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C13" s="5">
+        <v>6</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="5">
-        <v>5</v>
-      </c>
-      <c r="D11" s="5">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="5">
-        <v>6</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" s="5">
-        <v>1</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="5">
+        <v>7</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="5">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="5">
+        <v>8</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C17" s="5">
+        <v>9</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="5">
-        <v>7</v>
-      </c>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3">
-        <v>1</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="3">
-        <v>11001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="5">
-        <v>8</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1</v>
-      </c>
-      <c r="E14" s="5">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="3">
-        <v>11002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="5">
-        <v>9</v>
-      </c>
-      <c r="D15" s="5">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="5">
+      <c r="C19" s="5">
         <v>10</v>
       </c>
-      <c r="D16" s="5">
-        <v>1</v>
-      </c>
-      <c r="E16" s="5">
+      <c r="D19" s="5">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5">
         <v>2</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H19" s="5">
         <v>30020</v>
       </c>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="5">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C20" s="5">
         <v>11</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5">
-        <v>2</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="5">
-        <v>30021</v>
-      </c>
-      <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="5">
-        <v>12</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1</v>
-      </c>
-      <c r="E18" s="5">
-        <v>2</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="5">
-        <v>13</v>
-      </c>
-      <c r="D19" s="3">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3">
-        <v>2</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="5">
-        <v>14</v>
       </c>
       <c r="D20" s="5">
         <v>1</v>
@@ -914,36 +886,36 @@
         <v>2</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="H20" s="5">
+        <v>30021</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C21" s="5">
-        <v>15</v>
-      </c>
-      <c r="D21" s="3">
+        <v>12</v>
+      </c>
+      <c r="D21" s="5">
         <v>1</v>
       </c>
       <c r="E21" s="5">
         <v>2</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H21" s="5"/>
-      <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C22" s="5">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
@@ -952,16 +924,16 @@
         <v>2</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C23" s="5">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D23" s="5">
         <v>1</v>
@@ -970,30 +942,105 @@
         <v>2</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C24" s="5">
+        <v>15</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5">
+        <v>2</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C25" s="5">
+        <v>16</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5">
+        <v>2</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="5">
+        <v>16</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="5">
+        <v>17</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="3">
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
         <v>18</v>
       </c>
-      <c r="D24" s="3">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3">
         <v>2</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I24" s="3"/>
+      <c r="F28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1192,12 +1239,12 @@
   <sheetData>
     <row r="1" spans="3:8" x14ac:dyDescent="0.15">
       <c r="E1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="3:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="C3" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>1</v>
@@ -1266,10 +1313,10 @@
         <v>1000</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -1284,10 +1331,10 @@
         <v>1000</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7" s="5">
         <v>30002</v>

--- a/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="45">
   <si>
     <t>Id</t>
   </si>
@@ -78,9 +78,6 @@
     <t>Map</t>
   </si>
   <si>
-    <t>Map1</t>
-  </si>
-  <si>
     <t>Map2</t>
   </si>
   <si>
@@ -165,7 +162,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>#</t>
+    <t>Relationship</t>
+  </si>
+  <si>
+    <t>Relationship</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -557,7 +557,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E1" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -622,7 +622,7 @@
     </row>
     <row r="6" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="5">
         <v>1</v>
@@ -645,7 +645,7 @@
     </row>
     <row r="7" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B7" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -656,7 +656,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="5">
         <v>1</v>
@@ -726,10 +726,10 @@
         <v>1</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H11" s="5"/>
     </row>
@@ -762,10 +762,10 @@
         <v>1</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H13" s="5"/>
     </row>
@@ -780,39 +780,33 @@
         <v>1</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C15" s="5">
+        <v>8</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="5">
-        <v>7</v>
-      </c>
-      <c r="D15" s="3">
-        <v>1</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="C16" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="5">
         <v>1</v>
@@ -821,13 +815,16 @@
         <v>1</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="C17" s="5">
         <v>9</v>
       </c>
@@ -838,15 +835,15 @@
         <v>1</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -854,7 +851,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="5">
         <v>10</v>
@@ -924,10 +921,10 @@
         <v>2</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H22" s="5"/>
     </row>
@@ -960,10 +957,10 @@
         <v>2</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H24" s="5"/>
     </row>
@@ -978,19 +975,16 @@
         <v>2</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="C26" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D26" s="3">
         <v>1</v>
@@ -999,47 +993,47 @@
         <v>2</v>
       </c>
       <c r="F26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <v>18</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="5">
+        <v>18</v>
+      </c>
+      <c r="D28" s="5">
+        <v>1</v>
+      </c>
+      <c r="E28" s="5">
+        <v>2</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="5">
-        <v>17</v>
-      </c>
-      <c r="D27" s="5">
-        <v>1</v>
-      </c>
-      <c r="E27" s="5">
-        <v>2</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C28" s="3">
-        <v>18</v>
-      </c>
-      <c r="D28" s="3">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3">
-        <v>2</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1133,10 +1127,10 @@
         <v>3</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H6" s="5">
         <v>30300</v>
@@ -1153,10 +1147,10 @@
         <v>3</v>
       </c>
       <c r="F7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="H7" s="5">
         <v>30301</v>
@@ -1173,10 +1167,10 @@
         <v>3</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H8" s="5">
         <v>30302</v>
@@ -1193,10 +1187,10 @@
         <v>3</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H9" s="5">
         <v>30303</v>
@@ -1213,10 +1207,10 @@
         <v>3</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H10" s="5">
         <v>30304</v>
@@ -1239,12 +1233,12 @@
   <sheetData>
     <row r="1" spans="3:8" x14ac:dyDescent="0.15">
       <c r="E1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="3:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="C3" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>1</v>
@@ -1313,10 +1307,10 @@
         <v>1000</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -1331,10 +1325,10 @@
         <v>1000</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H7" s="5">
         <v>30002</v>
